--- a/analysis.xlsx
+++ b/analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_sokutei/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9180E41F-0354-6B4B-AFC8-C095B51880A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D153AA1F-28A6-A445-A71E-187C0AE76E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>

--- a/analysis.xlsx
+++ b/analysis.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_sokutei/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D153AA1F-28A6-A445-A71E-187C0AE76E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822F239E-2BE9-604A-A154-814188FEA275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="52">
   <si>
     <t>ch</t>
     <phoneticPr fontId="1"/>
@@ -185,12 +186,130 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>課題3</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">カダイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22Na</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンプトン端</t>
+    <rPh sb="5" eb="6">
+      <t xml:space="preserve">タン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実験値</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ジッケンチ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>keV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mec^2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後方散乱ピーク</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">コウホウ </t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t xml:space="preserve">サンラン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実験値</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ジッケン </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">アタイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>57Co</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>60Co</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>137Cs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実験から計算</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ジッケンカラノ </t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">ケイサン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実験からの計算</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ジッケンカラノ </t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t xml:space="preserve">ケイサン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課題4</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">カダイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FWHM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>√peak</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分解能</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ブンカイ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ノウリョク </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>z</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -203,6 +322,15 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -253,17 +381,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -614,7 +742,746 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Sheet3!$E$5:$E$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>515.6170807</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1277.694838</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>z</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1169.926266</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1331.579124</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>669.5721832</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$H$5:$H$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.10077216020760876</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.4765752437467669E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.4282463427099976E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.7809220531698971E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.1972221242502067E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1407-3D46-A5EC-96A2B191C744}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="953782208"/>
+        <c:axId val="954082048"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="953782208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="954082048"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="954082048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="953782208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet3!$I$5:$I$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>4.4038888793596818E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7976052219496606E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9236188564454289E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.7404161051413384E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.8645710707761918E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$H$5:$H$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.10077216020760876</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.4765752437467669E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.4282463427099976E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.7809220531698971E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.1972221242502067E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BCE9-7245-9EB3-DD27A43FFBD1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="954008896"/>
+        <c:axId val="974111616"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="954008896"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="974111616"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="974111616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="954008896"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1170,20 +2037,1052 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>831850</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>659493</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>488043</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1203,6 +3102,83 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>463550</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="グラフ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BD7499C-D0CA-8174-8714-0EA4A2131160}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>425450</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="グラフ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEFCB6A2-B300-890F-1B63-1BA12CEA5060}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1528,10 +3504,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDDC4F7-1C94-C84E-928F-3F14F658D6C5}">
-  <dimension ref="A2:F12"/>
+  <dimension ref="A2:J26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1539,7 +3520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="B3">
         <v>336</v>
       </c>
@@ -1553,7 +3534,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:8">
       <c r="B4">
         <v>138</v>
       </c>
@@ -1568,7 +3549,7 @@
         <v>-15.528022602339774</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:8">
       <c r="B5">
         <v>35</v>
       </c>
@@ -1587,7 +3568,7 @@
         <v>3.7878664857879132</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:8">
       <c r="B6">
         <v>308</v>
       </c>
@@ -1595,7 +3576,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:8">
       <c r="B7">
         <v>350</v>
       </c>
@@ -1603,7 +3584,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1614,7 +3595,15 @@
         <v>661.7</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="10" spans="1:8">
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="B11" t="s">
         <v>30</v>
       </c>
@@ -1623,18 +3612,275 @@
         <v>669.57218315265789</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:8">
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12">
         <f>SQRT((B9*E5)^2+F5^2)</f>
         <v>4.5642541425258649</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="H16">
+        <f>(G22-F4)/E4</f>
+        <v>59.335514784553816</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" t="s">
+        <v>40</v>
+      </c>
+      <c r="I19" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" t="s">
+        <v>0</v>
+      </c>
+      <c r="J20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21">
+        <v>511</v>
+      </c>
+      <c r="C21">
+        <f>B21/(1+$F$10/(2*B21))</f>
+        <v>340.66666666666669</v>
+      </c>
+      <c r="D21">
+        <v>95</v>
+      </c>
+      <c r="E21">
+        <f>D21*$E$4+$F$4</f>
+        <v>350.11534563768708</v>
+      </c>
+      <c r="F21">
+        <f>SQRT((D21*$E$5)^2+$F$5^2)</f>
+        <v>4.0243010879811072</v>
+      </c>
+      <c r="G21">
+        <f>B21/(1+(2*B21)/$F$10)</f>
+        <v>170.33333333333334</v>
+      </c>
+      <c r="H21">
+        <v>53</v>
+      </c>
+      <c r="I21">
+        <f>H21*$E$4+$F$4</f>
+        <v>188.46248809999099</v>
+      </c>
+      <c r="J21">
+        <f>SQRT((H21*$E$5)^2+$F$5^2)</f>
+        <v>3.8630073309544026</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="B22">
+        <v>1275</v>
+      </c>
+      <c r="C22">
+        <f t="shared" ref="C22:C26" si="0">B22/(1+$F$10/(2*B22))</f>
+        <v>1062.1528912120223</v>
+      </c>
+      <c r="D22">
+        <v>280</v>
+      </c>
+      <c r="E22">
+        <f>D22*$E$4+$F$4</f>
+        <v>1062.1576943156342</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ref="F22:F26" si="1">SQRT((D22*$E$5)^2+$F$5^2)</f>
+        <v>5.5130178128043523</v>
+      </c>
+      <c r="G22">
+        <f t="shared" ref="G22:G26" si="2">B22/(1+(2*B22)/$F$10)</f>
+        <v>212.84710878797779</v>
+      </c>
+      <c r="J22">
+        <f t="shared" ref="J22:J26" si="3">SQRT((H22*$E$5)^2+$F$5^2)</f>
+        <v>3.7878664857879132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23">
+        <v>122</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>39.427814569536423</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>3.7878664857879132</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="2"/>
+        <v>82.572185430463577</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="3"/>
+        <v>3.7878664857879132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24">
+        <v>1173</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>963.19845992299611</v>
+      </c>
+      <c r="D24">
+        <v>257</v>
+      </c>
+      <c r="E24">
+        <f t="shared" ref="E22:E26" si="4">D24*$E$4+$F$4</f>
+        <v>973.63351042594343</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>5.278787336188036</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="2"/>
+        <v>209.80154007700384</v>
+      </c>
+      <c r="H24">
+        <v>62</v>
+      </c>
+      <c r="I24">
+        <f t="shared" ref="I22:I26" si="5">H24*$E$4+$F$4</f>
+        <v>223.10238614378304</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="3"/>
+        <v>3.8903277384422768</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="B25">
+        <v>1333</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>1118.5955303745673</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="1"/>
+        <v>3.7878664857879132</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="2"/>
+        <v>214.4044696254328</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="3"/>
+        <v>3.7878664857879132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26">
+        <v>661.7</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>477.37340819886617</v>
+      </c>
+      <c r="D26">
+        <v>125</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="4"/>
+        <v>465.58167245032718</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="1"/>
+        <v>4.1887662539015809</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="2"/>
+        <v>184.32659180113387</v>
+      </c>
+      <c r="H26">
+        <v>56</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="5"/>
+        <v>200.00912078125501</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="3"/>
+        <v>3.8716598287764108</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -1651,48 +3897,48 @@
     </row>
     <row r="2" spans="1:9" ht="21" thickBot="1"/>
     <row r="3" spans="1:9">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>0.9999792773666133</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>0.99995855516265408</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>0.99994474021687207</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>3.9993140911977223</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="21" thickBot="1">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>5</v>
       </c>
     </row>
@@ -1702,156 +3948,154 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <v>1157720.8164603997</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>1157720.8164603997</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <v>72382.372753713295</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12">
         <v>1.132400162722055E-7</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13">
         <v>3</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13">
         <v>47.983539600157989</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>15.994513200052664</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="21" thickBot="1">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>4</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>1157768.7999999998</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="21" thickBot="1"/>
     <row r="16" spans="1:9">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17">
         <v>-15.528022602339774</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17">
         <v>3.7878664857879132</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17">
         <v>-4.0994112808888499</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17">
         <v>2.6260344312889514E-2</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17">
         <v>-27.582704304943505</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17">
         <v>-3.4733408997360429</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17">
         <v>-27.582704304943505</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17">
         <v>-3.4733408997360429</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="21" thickBot="1">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>3.8488775604213354</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <v>1.4305982448012507E-2</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <v>269.03972337503109</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>1.132400162722055E-7</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="1">
         <v>3.8033495394362045</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="1">
         <v>3.8944055814064664</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>3.8033495394362045</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="1">
         <v>3.8944055814064664</v>
       </c>
     </row>
@@ -1859,4 +4103,244 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40D0D7B9-E557-2D4E-99FA-2320A9CF6E7F}">
+  <dimension ref="B2:K10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetData>
+    <row r="2" spans="2:11">
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11">
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5">
+        <v>511</v>
+      </c>
+      <c r="D5">
+        <v>138</v>
+      </c>
+      <c r="E5">
+        <f>D5*$J$5+$K$5</f>
+        <v>515.61708073580451</v>
+      </c>
+      <c r="F5">
+        <v>13.5</v>
+      </c>
+      <c r="G5">
+        <f>$J$5*F5</f>
+        <v>51.959847065688031</v>
+      </c>
+      <c r="H5">
+        <f>G5/E5</f>
+        <v>0.10077216020760876</v>
+      </c>
+      <c r="I5">
+        <f>1/SQRT(E5)</f>
+        <v>4.4038888793596818E-2</v>
+      </c>
+      <c r="J5">
+        <v>3.8488775604213354</v>
+      </c>
+      <c r="K5">
+        <v>-15.528022602339774</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="C6">
+        <v>1275</v>
+      </c>
+      <c r="D6">
+        <v>336</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ref="E6:E10" si="0">D6*$J$5+$K$5</f>
+        <v>1277.6948376992291</v>
+      </c>
+      <c r="F6">
+        <v>21.5</v>
+      </c>
+      <c r="G6">
+        <f t="shared" ref="G6:G10" si="1">$J$5*F6</f>
+        <v>82.750867549058711</v>
+      </c>
+      <c r="H6">
+        <f t="shared" ref="H6:H10" si="2">G6/E6</f>
+        <v>6.4765752437467669E-2</v>
+      </c>
+      <c r="I6">
+        <f t="shared" ref="I6:I10" si="3">1/SQRT(E6)</f>
+        <v>2.7976052219496606E-2</v>
+      </c>
+      <c r="J6">
+        <v>1.4305982448012507E-2</v>
+      </c>
+      <c r="K6">
+        <v>3.7878664857879132</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7">
+        <v>122</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7">
+        <v>4.5</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>17.319949021896008</v>
+      </c>
+      <c r="H7" t="e">
+        <f>G7/E7</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I7" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>1173</v>
+      </c>
+      <c r="D8">
+        <v>308</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>1169.9262660074314</v>
+      </c>
+      <c r="F8">
+        <v>16.5</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>63.506479746952031</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="2"/>
+        <v>5.4282463427099976E-2</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="3"/>
+        <v>2.9236188564454289E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="C9">
+        <v>1333</v>
+      </c>
+      <c r="D9">
+        <v>350</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>1331.5791235451275</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>76.977551208426704</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>5.7809220531698971E-2</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="3"/>
+        <v>2.7404161051413384E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10">
+        <v>661.7</v>
+      </c>
+      <c r="D10">
+        <v>178</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>669.57218315265789</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>61.582040966741367</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="2"/>
+        <v>9.1972221242502067E-2</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="3"/>
+        <v>3.8645710707761918E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/analysis.xlsx
+++ b/analysis.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_sokutei/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822F239E-2BE9-604A-A154-814188FEA275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBB472C-5DB9-BA4A-A94E-33D08CAD27C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="3" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="56">
   <si>
     <t>ch</t>
     <phoneticPr fontId="1"/>
@@ -304,6 +306,34 @@
     <t>z</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>時間較正</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ジカンコウセイ </t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ns</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遅延時間</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">チエンジカン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>係数</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ケイスウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -377,7 +407,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -392,6 +422,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1401,6 +1443,423 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet4!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ns</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet4!$B$5:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>232</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>259</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet4!$C$5:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>356</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>406</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>456</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>506</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5692-044D-AF10-9E51E174BAAC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="927528960"/>
+        <c:axId val="916368320"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="927528960"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="916368320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="916368320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927528960"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1521,6 +1980,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2554,6 +3053,522 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3179,6 +4194,47 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="グラフ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCD6DD11-CD09-E41B-13BC-6DD022229FD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3502,6 +4558,26 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{0BFBD2B6-D187-DA4E-BCCC-3AD3051F9903}">
+  <we:reference id="WA104100404" version="3.0.0.1" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA104100404" version="3.0.0.1" store="WA104100404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDDC4F7-1C94-C84E-928F-3F14F658D6C5}">
   <dimension ref="A2:J26"/>
@@ -3795,7 +4871,7 @@
         <v>257</v>
       </c>
       <c r="E24">
-        <f t="shared" ref="E22:E26" si="4">D24*$E$4+$F$4</f>
+        <f t="shared" ref="E24:E26" si="4">D24*$E$4+$F$4</f>
         <v>973.63351042594343</v>
       </c>
       <c r="F24">
@@ -3810,7 +4886,7 @@
         <v>62</v>
       </c>
       <c r="I24">
-        <f t="shared" ref="I22:I26" si="5">H24*$E$4+$F$4</f>
+        <f t="shared" ref="I24:I26" si="5">H24*$E$4+$F$4</f>
         <v>223.10238614378304</v>
       </c>
       <c r="J24">
@@ -4343,4 +5419,349 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A92B69F-F9F6-E546-ABE7-BAC8EC966A13}">
+  <dimension ref="A2:F14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1.9230217530069063</v>
+      </c>
+      <c r="F4" s="5">
+        <v>9.4693284754248452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>50</v>
+      </c>
+      <c r="C6">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>76</v>
+      </c>
+      <c r="C7">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>102</v>
+      </c>
+      <c r="C8">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9">
+        <v>128</v>
+      </c>
+      <c r="C9">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10">
+        <v>154</v>
+      </c>
+      <c r="C10">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11">
+        <v>180</v>
+      </c>
+      <c r="C11">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12">
+        <v>206</v>
+      </c>
+      <c r="C12">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13">
+        <v>232</v>
+      </c>
+      <c r="C13">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14">
+        <v>259</v>
+      </c>
+      <c r="C14">
+        <v>506</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A53BCD90-B5DB-234B-AAFE-811482D928C8}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="21" thickBot="1"/>
+    <row r="3" spans="1:9">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.99998565567891595</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.99997131156359154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.99996772550904045</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.8600138087010355</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="21" thickBot="1">
+      <c r="A8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="21" thickBot="1">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>206244.08300999075</v>
+      </c>
+      <c r="D12" s="5">
+        <v>206244.08300999075</v>
+      </c>
+      <c r="E12" s="5">
+        <v>278850.0000000156</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1.8522114878870002E-19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>5.9169900092516903</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.73962375115646128</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" ht="21" thickBot="1">
+      <c r="A14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>206250</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" ht="21" thickBot="1"/>
+    <row r="16" spans="1:9">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5">
+        <v>9.4693284754248452</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.58169221916100677</v>
+      </c>
+      <c r="D17" s="5">
+        <v>16.278932678664258</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2.0403247101735171E-7</v>
+      </c>
+      <c r="F17" s="5">
+        <v>8.1279438126234744</v>
+      </c>
+      <c r="G17" s="5">
+        <v>10.810713138226216</v>
+      </c>
+      <c r="H17" s="5">
+        <v>8.1279438126234744</v>
+      </c>
+      <c r="I17" s="5">
+        <v>10.810713138226216</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="21" thickBot="1">
+      <c r="A18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="6">
+        <v>1.9230217530069063</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3.6416556117431337E-3</v>
+      </c>
+      <c r="D18" s="6">
+        <v>528.06249630135198</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.8522114878870134E-19</v>
+      </c>
+      <c r="F18" s="6">
+        <v>1.9146240801072372</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1.9314194259065753</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1.9146240801072372</v>
+      </c>
+      <c r="I18" s="6">
+        <v>1.9314194259065753</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>
--- a/analysis.xlsx
+++ b/analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasaray/Desktop/TeX/Physics_Laboratory/douji_sokutei/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBB472C-5DB9-BA4A-A94E-33D08CAD27C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D8761B-CB27-F842-BF84-3F66C27A07DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="3" xr2:uid="{10402794-AE0E-6B4D-9BC0-982A88CB420E}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="55">
   <si>
     <t>ch</t>
     <phoneticPr fontId="1"/>
@@ -300,10 +300,6 @@
     <rPh sb="2" eb="3">
       <t xml:space="preserve">ノウリョク </t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>z</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -860,30 +856,31 @@
             </c:spPr>
           </c:marker>
           <c:xVal>
-            <c:strRef>
+            <c:numRef>
               <c:f>Sheet3!$E$5:$E$10</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>515.6170807</c:v>
+                  <c:v>515.61708073580451</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1277.694838</c:v>
+                  <c:v>1277.6948376992291</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>z</c:v>
+                  <c:v>119.18269201240696</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1169.926266</c:v>
+                  <c:v>1169.9262660074314</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1331.579124</c:v>
+                  <c:v>1331.5791235451275</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>669.5721832</c:v>
+                  <c:v>669.57218315265789</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
@@ -898,7 +895,7 @@
                   <c:v>6.4765752437467669E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.14532268678822086</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5.4282463427099976E-2</c:v>
@@ -1208,7 +1205,7 @@
                   <c:v>2.7976052219496606E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>9.1599563607362294E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2.9236188564454289E-2</c:v>
@@ -1235,7 +1232,7 @@
                   <c:v>6.4765752437467669E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.14532268678822086</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5.4282463427099976E-2</c:v>
@@ -4206,16 +4203,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>412750</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>863600</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>196850</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4809,7 +4806,7 @@
         <v>1275</v>
       </c>
       <c r="C22">
-        <f t="shared" ref="C22:C26" si="0">B22/(1+$F$10/(2*B22))</f>
+        <f>B22/(1+$F$10/(2*B22))</f>
         <v>1062.1528912120223</v>
       </c>
       <c r="D22">
@@ -4820,15 +4817,15 @@
         <v>1062.1576943156342</v>
       </c>
       <c r="F22">
-        <f t="shared" ref="F22:F26" si="1">SQRT((D22*$E$5)^2+$F$5^2)</f>
+        <f t="shared" ref="F22:F26" si="0">SQRT((D22*$E$5)^2+$F$5^2)</f>
         <v>5.5130178128043523</v>
       </c>
       <c r="G22">
-        <f t="shared" ref="G22:G26" si="2">B22/(1+(2*B22)/$F$10)</f>
+        <f>B22/(1+(2*B22)/$F$10)</f>
         <v>212.84710878797779</v>
       </c>
       <c r="J22">
-        <f t="shared" ref="J22:J26" si="3">SQRT((H22*$E$5)^2+$F$5^2)</f>
+        <f t="shared" ref="J22:J26" si="1">SQRT((H22*$E$5)^2+$F$5^2)</f>
         <v>3.7878664857879132</v>
       </c>
     </row>
@@ -4840,19 +4837,19 @@
         <v>122</v>
       </c>
       <c r="C23">
+        <f t="shared" ref="C22:C26" si="2">B23/(1+$F$10/(2*B23))</f>
+        <v>39.427814569536423</v>
+      </c>
+      <c r="F23">
         <f t="shared" si="0"/>
-        <v>39.427814569536423</v>
-      </c>
-      <c r="F23">
+        <v>3.7878664857879132</v>
+      </c>
+      <c r="G23">
+        <f t="shared" ref="G22:G26" si="3">B23/(1+(2*B23)/$F$10)</f>
+        <v>82.572185430463577</v>
+      </c>
+      <c r="J23">
         <f t="shared" si="1"/>
-        <v>3.7878664857879132</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="2"/>
-        <v>82.572185430463577</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="3"/>
         <v>3.7878664857879132</v>
       </c>
     </row>
@@ -4864,7 +4861,7 @@
         <v>1173</v>
       </c>
       <c r="C24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>963.19845992299611</v>
       </c>
       <c r="D24">
@@ -4875,11 +4872,11 @@
         <v>973.63351042594343</v>
       </c>
       <c r="F24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.278787336188036</v>
       </c>
       <c r="G24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>209.80154007700384</v>
       </c>
       <c r="H24">
@@ -4890,7 +4887,7 @@
         <v>223.10238614378304</v>
       </c>
       <c r="J24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3.8903277384422768</v>
       </c>
     </row>
@@ -4899,19 +4896,19 @@
         <v>1333</v>
       </c>
       <c r="C25">
+        <f t="shared" si="2"/>
+        <v>1118.5955303745673</v>
+      </c>
+      <c r="F25">
         <f t="shared" si="0"/>
-        <v>1118.5955303745673</v>
-      </c>
-      <c r="F25">
+        <v>3.7878664857879132</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="3"/>
+        <v>214.4044696254328</v>
+      </c>
+      <c r="J25">
         <f t="shared" si="1"/>
-        <v>3.7878664857879132</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="2"/>
-        <v>214.4044696254328</v>
-      </c>
-      <c r="J25">
-        <f t="shared" si="3"/>
         <v>3.7878664857879132</v>
       </c>
     </row>
@@ -4923,7 +4920,7 @@
         <v>661.7</v>
       </c>
       <c r="C26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>477.37340819886617</v>
       </c>
       <c r="D26">
@@ -4934,11 +4931,11 @@
         <v>465.58167245032718</v>
       </c>
       <c r="F26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4.1887662539015809</v>
       </c>
       <c r="G26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>184.32659180113387</v>
       </c>
       <c r="H26">
@@ -4949,7 +4946,7 @@
         <v>200.00912078125501</v>
       </c>
       <c r="J26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3.8716598287764108</v>
       </c>
     </row>
@@ -5273,22 +5270,22 @@
         <v>336</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6:E10" si="0">D6*$J$5+$K$5</f>
+        <f>D6*$J$5+$K$5</f>
         <v>1277.6948376992291</v>
       </c>
       <c r="F6">
         <v>21.5</v>
       </c>
       <c r="G6">
-        <f t="shared" ref="G6:G10" si="1">$J$5*F6</f>
+        <f t="shared" ref="G6:G10" si="0">$J$5*F6</f>
         <v>82.750867549058711</v>
       </c>
       <c r="H6">
-        <f t="shared" ref="H6:H10" si="2">G6/E6</f>
+        <f t="shared" ref="H6:H10" si="1">G6/E6</f>
         <v>6.4765752437467669E-2</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I10" si="3">1/SQRT(E6)</f>
+        <f t="shared" ref="I6:I10" si="2">1/SQRT(E6)</f>
         <v>2.7976052219496606E-2</v>
       </c>
       <c r="J6">
@@ -5308,23 +5305,24 @@
       <c r="D7">
         <v>35</v>
       </c>
-      <c r="E7" t="s">
-        <v>51</v>
+      <c r="E7">
+        <f>D7*$J$5+$K$5</f>
+        <v>119.18269201240696</v>
       </c>
       <c r="F7">
         <v>4.5</v>
       </c>
       <c r="G7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>17.319949021896008</v>
       </c>
-      <c r="H7" t="e">
+      <c r="H7">
         <f>G7/E7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I7" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>0.14532268678822086</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>9.1599563607362294E-2</v>
       </c>
     </row>
     <row r="8" spans="2:11">
@@ -5338,22 +5336,22 @@
         <v>308</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E6:E10" si="3">D8*$J$5+$K$5</f>
         <v>1169.9262660074314</v>
       </c>
       <c r="F8">
         <v>16.5</v>
       </c>
       <c r="G8">
+        <f t="shared" si="0"/>
+        <v>63.506479746952031</v>
+      </c>
+      <c r="H8">
         <f t="shared" si="1"/>
-        <v>63.506479746952031</v>
-      </c>
-      <c r="H8">
+        <v>5.4282463427099976E-2</v>
+      </c>
+      <c r="I8">
         <f t="shared" si="2"/>
-        <v>5.4282463427099976E-2</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="3"/>
         <v>2.9236188564454289E-2</v>
       </c>
     </row>
@@ -5365,22 +5363,22 @@
         <v>350</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1331.5791235451275</v>
       </c>
       <c r="F9">
         <v>20</v>
       </c>
       <c r="G9">
+        <f t="shared" si="0"/>
+        <v>76.977551208426704</v>
+      </c>
+      <c r="H9">
         <f t="shared" si="1"/>
-        <v>76.977551208426704</v>
-      </c>
-      <c r="H9">
+        <v>5.7809220531698971E-2</v>
+      </c>
+      <c r="I9">
         <f t="shared" si="2"/>
-        <v>5.7809220531698971E-2</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="3"/>
         <v>2.7404161051413384E-2</v>
       </c>
     </row>
@@ -5395,22 +5393,22 @@
         <v>178</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>669.57218315265789</v>
       </c>
       <c r="F10">
         <v>16</v>
       </c>
       <c r="G10">
+        <f t="shared" si="0"/>
+        <v>61.582040966741367</v>
+      </c>
+      <c r="H10">
         <f t="shared" si="1"/>
-        <v>61.582040966741367</v>
-      </c>
-      <c r="H10">
+        <v>9.1972221242502067E-2</v>
+      </c>
+      <c r="I10">
         <f t="shared" si="2"/>
-        <v>9.1972221242502067E-2</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="3"/>
         <v>3.8645710707761918E-2</v>
       </c>
     </row>
@@ -5423,20 +5421,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A92B69F-F9F6-E546-ABE7-BAC8EC966A13}">
-  <dimension ref="A2:F14"/>
+  <dimension ref="A2:F16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
         <v>54</v>
-      </c>
-      <c r="E3" t="s">
-        <v>55</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -5447,7 +5445,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" s="5">
         <v>1.9230217530069063</v>
@@ -5495,6 +5493,9 @@
       <c r="C9">
         <v>256</v>
       </c>
+      <c r="E9">
+        <v>11.3</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10">
@@ -5503,6 +5504,10 @@
       <c r="C10">
         <v>306</v>
       </c>
+      <c r="E10">
+        <f>E9*E4</f>
+        <v>21.73014580897804</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11">
@@ -5519,6 +5524,9 @@
       <c r="C12">
         <v>406</v>
       </c>
+      <c r="E12">
+        <v>6.4219999999999997</v>
+      </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13">
@@ -5527,6 +5535,10 @@
       <c r="C13">
         <v>456</v>
       </c>
+      <c r="E13">
+        <f>E12*E4</f>
+        <v>12.349645697810351</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14">
@@ -5534,6 +5546,17 @@
       </c>
       <c r="C14">
         <v>506</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="E15">
+        <v>6.7389999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="E16">
+        <f>E4*E15</f>
+        <v>12.959243593513541</v>
       </c>
     </row>
   </sheetData>
